--- a/data/trans_orig/P32D_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32D_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses ha tomado 6/5 (Hombre/Mujer) o más bebidas estándar en una misma ocasión en 2023</t>
+          <t>Población según si en los últimos 12 meses ha tomado 6/5 (Hombre/Mujer) o más bebidas estándar en una misma ocasión en 2023 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>64192</t>
+          <t>66391</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>111381</t>
+          <t>107523</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>54648</t>
+          <t>53749</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>76107</t>
+          <t>75543</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,89%</t>
+          <t>47,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>126802</t>
+          <t>127241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>173111</t>
+          <t>175314</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,26%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>106852</t>
+          <t>109759</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145863</t>
+          <t>148036</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>32,17%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>44,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45202</t>
+          <t>45466</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66368</t>
+          <t>66555</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>160873</t>
+          <t>158349</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>203470</t>
+          <t>204217</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,59%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>57879</t>
+          <t>58637</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93909</t>
+          <t>91406</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>17807</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36049</t>
+          <t>35821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>84052</t>
+          <t>80983</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>121591</t>
+          <t>118903</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,22%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22563</t>
+          <t>23790</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9436</t>
+          <t>8894</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>26255</t>
+          <t>25692</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9220</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25876</t>
+          <t>24736</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10526</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>13102</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32202</t>
+          <t>30960</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3899</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6719</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26416</t>
+          <t>26156</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>459</t>
+          <t>681</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6095</t>
+          <t>6378</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1443,12 +1443,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>577</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6114</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>1781</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9534</t>
+          <t>8811</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1493,12 +1493,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7273</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1556,62 +1556,62 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>2233</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1225</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>7144</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>2233</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>7880</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>1710</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9620</t>
+          <t>9013</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1684,12 +1684,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1572</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9647</t>
+          <t>9239</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76550</t>
+          <t>76219</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>124865</t>
+          <t>120843</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60084</t>
+          <t>59090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>84615</t>
+          <t>83823</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142965</t>
+          <t>146698</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>194091</t>
+          <t>196154</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>178071</t>
+          <t>179288</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>229530</t>
+          <t>229403</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54668</t>
+          <t>54531</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>77549</t>
+          <t>77929</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>242666</t>
+          <t>241438</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>297981</t>
+          <t>297998</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77765</t>
+          <t>75444</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118873</t>
+          <t>118047</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25030</t>
+          <t>24955</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47077</t>
+          <t>46730</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108103</t>
+          <t>108705</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155184</t>
+          <t>153356</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -2203,12 +2203,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29844</t>
+          <t>29860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74444</t>
+          <t>75098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2238,12 +2238,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>4157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15021</t>
+          <t>14456</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2273,12 +2273,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37883</t>
+          <t>38345</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>86000</t>
+          <t>81948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -2316,12 +2316,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25346</t>
+          <t>24022</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>6126</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18468</t>
+          <t>18436</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2366,12 +2366,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>14410</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35532</t>
+          <t>36178</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,36%</t>
         </is>
       </c>
     </row>
@@ -2429,12 +2429,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3626</t>
+          <t>3936</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17231</t>
+          <t>18006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2444,12 +2444,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5146</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18353</t>
+          <t>17915</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10904</t>
+          <t>11588</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28644</t>
+          <t>28050</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2514,12 +2514,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>647</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7723</t>
+          <t>7655</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2557,12 +2557,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2577,12 +2577,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2612,12 +2612,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>995</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8229</t>
+          <t>8277</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7879</t>
+          <t>8211</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2690,62 +2690,62 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2449</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>1334</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>8153</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>8550</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1838</t>
+          <t>2134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>11566</t>
+          <t>10927</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2783,12 +2783,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4346</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3170</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13543</t>
+          <t>13352</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>50677</t>
+          <t>49843</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>86738</t>
+          <t>84675</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>146334</t>
+          <t>143043</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>346107</t>
+          <t>348516</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3068,12 +3068,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>183921</t>
+          <t>185017</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>529510</t>
+          <t>537141</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3083,12 +3083,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,23%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>75,52%</t>
+          <t>76,61%</t>
         </is>
       </c>
     </row>
@@ -3111,12 +3111,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>124946</t>
+          <t>124982</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>165460</t>
+          <t>166981</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3126,12 +3126,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,37%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>51,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17832</t>
+          <t>17785</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>148204</t>
+          <t>153237</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,48%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>99434</t>
+          <t>98644</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>304768</t>
+          <t>308308</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,97%</t>
         </is>
       </c>
     </row>
@@ -3224,12 +3224,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>46890</t>
+          <t>47193</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>82580</t>
+          <t>80748</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>5825</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58865</t>
+          <t>62105</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>16,54%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>34221</t>
+          <t>35531</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>130905</t>
+          <t>128099</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3309,12 +3309,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,27%</t>
         </is>
       </c>
     </row>
@@ -3337,12 +3337,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>17476</t>
+          <t>16145</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46267</t>
+          <t>44890</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>17919</t>
+          <t>18625</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3387,12 +3387,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>12292</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>59705</t>
+          <t>57928</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3450,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4011</t>
+          <t>4050</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16748</t>
+          <t>16849</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3465,12 +3465,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14414</t>
+          <t>14571</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>3509</t>
+          <t>2781</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>21828</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3535,12 +3535,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3563,12 +3563,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>7104</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24360</t>
+          <t>24170</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3578,12 +3578,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6940</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>27176</t>
+          <t>26953</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3648,12 +3648,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -3676,97 +3676,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>1161</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>2057</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>7736</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,31%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>1161</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>7799</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>6374</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>1161</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>6533</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3809,7 +3809,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3824,62 +3824,62 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>2905</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>5722</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>861</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>4973</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6336</t>
+          <t>5462</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3937,62 +3937,62 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>2905</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>6216</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>1208</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>6117</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>82004</t>
+          <t>81983</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>120462</t>
+          <t>117805</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4167,12 +4167,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>121694</t>
+          <t>122975</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>153800</t>
+          <t>153895</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>213029</t>
+          <t>215422</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>260286</t>
+          <t>263893</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,6%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,26%</t>
         </is>
       </c>
     </row>
@@ -4245,12 +4245,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>139785</t>
+          <t>141368</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>182075</t>
+          <t>179758</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>31,82%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,45%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4280,12 +4280,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>62946</t>
+          <t>63066</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>89608</t>
+          <t>89247</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4295,12 +4295,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4315,12 +4315,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>212408</t>
+          <t>214139</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>262305</t>
+          <t>261470</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4330,12 +4330,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,19%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,93%</t>
         </is>
       </c>
     </row>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>77210</t>
+          <t>77293</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>115278</t>
+          <t>116878</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4373,12 +4373,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>34577</t>
+          <t>34235</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>57392</t>
+          <t>57203</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>118468</t>
+          <t>118976</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>163442</t>
+          <t>162599</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,34%</t>
         </is>
       </c>
     </row>
@@ -4471,12 +4471,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>20520</t>
+          <t>19594</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>43429</t>
+          <t>42352</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>19512</t>
+          <t>19608</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>30368</t>
+          <t>29891</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>57305</t>
+          <t>56075</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -4584,12 +4584,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>15149</t>
+          <t>16068</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>38887</t>
+          <t>40002</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4599,12 +4599,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>14067</t>
+          <t>15127</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>20351</t>
+          <t>21509</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>44909</t>
+          <t>47189</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -4697,12 +4697,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>12504</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>30375</t>
+          <t>31091</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2746</t>
+          <t>2772</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>16797</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>42782</t>
+          <t>38276</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4810,97 +4810,97 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>1753</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>2748</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>0,21%</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="R40" s="2" t="inlineStr">
         <is>
           <t>616</t>
         </is>
       </c>
-      <c r="L40" s="2" t="inlineStr">
+      <c r="S40" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M40" s="2" t="inlineStr">
-        <is>
-          <t>2368</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>2842</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P40" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>2430</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -4928,7 +4928,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>3660</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4958,62 +4958,62 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>722</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>1325</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>4124</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O41" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q41" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R41" s="2" t="inlineStr">
-        <is>
-          <t>722</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T41" s="2" t="inlineStr">
-        <is>
-          <t>3862</t>
-        </is>
-      </c>
-      <c r="U41" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="V41" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5036,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3486</t>
+          <t>3829</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>14935</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>971</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6527</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>19556</t>
+          <t>19569</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>309402</t>
+          <t>307992</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>388854</t>
+          <t>387547</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>419980</t>
+          <t>422717</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>758170</t>
+          <t>751416</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>729855</t>
+          <t>733316</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1312763</t>
+          <t>1398915</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>53,9%</t>
         </is>
       </c>
     </row>
@@ -5379,12 +5379,12 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>591606</t>
+          <t>592431</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>677629</t>
+          <t>681719</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5394,12 +5394,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5414,12 +5414,12 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>146035</t>
+          <t>148682</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>336124</t>
+          <t>336556</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5449,12 +5449,12 @@
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>687339</t>
+          <t>657914</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>993364</t>
+          <t>997132</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -5492,12 +5492,12 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>293663</t>
+          <t>293479</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>366923</t>
+          <t>366401</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5507,12 +5507,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5527,12 +5527,12 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>68093</t>
+          <t>75521</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>170117</t>
+          <t>168930</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5562,12 +5562,12 @@
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>337885</t>
+          <t>324634</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>515023</t>
+          <t>508338</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -5605,12 +5605,12 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>94259</t>
+          <t>93262</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>153133</t>
+          <t>153409</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5620,12 +5620,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5640,12 +5640,12 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>42022</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
@@ -5655,12 +5655,12 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5675,12 +5675,12 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>110020</t>
+          <t>108593</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>180423</t>
+          <t>180258</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5718,12 +5718,12 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>45328</t>
+          <t>46504</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>82586</t>
+          <t>81747</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -5733,12 +5733,12 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>40107</t>
+          <t>38885</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -5768,12 +5768,12 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>63503</t>
+          <t>63380</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>111173</t>
+          <t>109674</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -5831,12 +5831,12 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>37933</t>
+          <t>37982</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>68484</t>
+          <t>68339</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5846,12 +5846,12 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>9442</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>53246</t>
+          <t>53457</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>95882</t>
+          <t>93757</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
@@ -5916,12 +5916,12 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -5944,12 +5944,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>10199</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -5959,12 +5959,12 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1106</t>
+          <t>1173</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>9979</t>
+          <t>9051</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5999,7 +5999,7 @@
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5127</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>16382</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -6029,12 +6029,12 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -6057,12 +6057,12 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2670</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>2571</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>14068</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -6170,12 +6170,12 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>12064</t>
+          <t>12197</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>29584</t>
+          <t>28274</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1681</t>
+          <t>1611</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>9518</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>15206</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>34160</t>
+          <t>33648</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -6255,12 +6255,12 @@
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32D_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P32D_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>83152</t>
+          <t>85466</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>66391</t>
+          <t>68700</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>107523</t>
+          <t>109164</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,38%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>64928</t>
+          <t>67417</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>53749</t>
+          <t>56306</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75543</t>
+          <t>78501</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>148080</t>
+          <t>152883</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>127241</t>
+          <t>132578</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175314</t>
+          <t>176685</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,7%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>126781</t>
+          <t>136062</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109759</t>
+          <t>116723</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>148036</t>
+          <t>156511</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55246</t>
+          <t>61417</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>45466</t>
+          <t>51219</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66555</t>
+          <t>73163</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,61%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>182026</t>
+          <t>197478</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158349</t>
+          <t>173911</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>204217</t>
+          <t>219340</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>74096</t>
+          <t>81947</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>58637</t>
+          <t>65167</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>91406</t>
+          <t>100945</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>25829</t>
+          <t>29769</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17807</t>
+          <t>21356</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>35821</t>
+          <t>40507</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>99924</t>
+          <t>111717</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80983</t>
+          <t>93142</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118903</t>
+          <t>135336</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>25,81%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13932</t>
+          <t>13905</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23790</t>
+          <t>22252</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2098</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16030</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>8874</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25692</t>
+          <t>25798</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>15321</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24736</t>
+          <t>24602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2304</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10373</t>
+          <t>11177</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>21010</t>
+          <t>20933</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13102</t>
+          <t>13681</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>30960</t>
+          <t>31844</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9974</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>3707</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>21439</t>
+          <t>24847</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1003</t>
+          <t>759</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>7492</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>12680</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>6188</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>26156</t>
+          <t>27137</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>678</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6378</t>
+          <t>6078</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,17 +1438,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2156</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>577</t>
+          <t>661</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5801</t>
+          <t>7053</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1458,12 +1458,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8811</t>
+          <t>9326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1526,12 +1526,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>8919</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2233</t>
+          <t>2504</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>7144</t>
+          <t>8426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1629,17 +1629,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1847</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9013</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1649,12 +1649,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1699,17 +1699,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>4492</t>
+          <t>4767</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1572</t>
+          <t>1806</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1719,12 +1719,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -1742,17 +1742,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>332109</t>
+          <t>352358</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>332109</t>
+          <t>352358</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>332109</t>
+          <t>352358</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,17 +1777,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>158911</t>
+          <t>171921</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158911</t>
+          <t>171921</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158911</t>
+          <t>171921</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,17 +1812,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>491019</t>
+          <t>524279</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>491019</t>
+          <t>524279</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>491019</t>
+          <t>524279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>96820</t>
+          <t>96204</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>76219</t>
+          <t>76668</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120843</t>
+          <t>116710</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>71817</t>
+          <t>78555</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>59090</t>
+          <t>65388</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>83823</t>
+          <t>91798</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>168637</t>
+          <t>174759</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>146698</t>
+          <t>151344</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>196154</t>
+          <t>201273</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>204727</t>
+          <t>220249</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>179288</t>
+          <t>195989</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>229403</t>
+          <t>245984</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>44,18%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,34%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>65670</t>
+          <t>72901</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>54531</t>
+          <t>59657</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>77929</t>
+          <t>85926</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>270397</t>
+          <t>293149</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>241438</t>
+          <t>264524</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>297998</t>
+          <t>319699</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,58%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>36,62%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,26%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>95676</t>
+          <t>104622</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>75444</t>
+          <t>85359</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118047</t>
+          <t>126921</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>34298</t>
+          <t>37895</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>24955</t>
+          <t>29020</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46730</t>
+          <t>52416</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>129974</t>
+          <t>142517</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>108705</t>
+          <t>120796</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>153356</t>
+          <t>168325</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>44699</t>
+          <t>38583</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29860</t>
+          <t>27587</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75098</t>
+          <t>54179</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8225</t>
+          <t>9343</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4157</t>
+          <t>4799</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14456</t>
+          <t>17099</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>52924</t>
+          <t>47927</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38345</t>
+          <t>35790</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>81948</t>
+          <t>63430</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -2311,32 +2311,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12523</t>
+          <t>18486</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>24022</t>
+          <t>33517</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10630</t>
+          <t>11598</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6126</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18436</t>
+          <t>19717</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>23152</t>
+          <t>30083</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14410</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36178</t>
+          <t>44998</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -2424,32 +2424,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8525</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3936</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>18153</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2459,32 +2459,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9574</t>
+          <t>12050</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17915</t>
+          <t>21053</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,32 +2494,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>18099</t>
+          <t>20953</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11588</t>
+          <t>13160</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28050</t>
+          <t>32086</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -2537,32 +2537,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>810</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7655</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2607,32 +2607,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3270</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>801</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8277</t>
+          <t>7777</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -2650,102 +2650,102 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>2696</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10785</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>8211</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>9822</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>2449</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>8153</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -2763,32 +2763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10927</t>
+          <t>11814</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1392</t>
+          <t>1546</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,22 +2833,22 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>6724</t>
+          <t>7039</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3323</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13352</t>
+          <t>14299</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2876,17 +2876,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>473916</t>
+          <t>498508</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>473916</t>
+          <t>498508</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>473916</t>
+          <t>498508</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,17 +2911,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>201606</t>
+          <t>223887</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>201606</t>
+          <t>223887</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>201606</t>
+          <t>223887</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>675522</t>
+          <t>722395</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>675522</t>
+          <t>722395</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>675522</t>
+          <t>722395</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2993,32 +2993,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>66521</t>
+          <t>68785</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>53905</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>84675</t>
+          <t>87840</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3028,32 +3028,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>274169</t>
+          <t>79792</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>143043</t>
+          <t>66693</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>348516</t>
+          <t>94430</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>73,03%</t>
+          <t>39,81%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3063,32 +3063,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>340690</t>
+          <t>148578</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>185017</t>
+          <t>128604</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>537141</t>
+          <t>172869</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>30,82%</t>
         </is>
       </c>
     </row>
@@ -3106,32 +3106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>145069</t>
+          <t>158523</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>124982</t>
+          <t>136174</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>166981</t>
+          <t>179232</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>49,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3141,32 +3141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>64966</t>
+          <t>73934</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17785</t>
+          <t>61321</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>153237</t>
+          <t>86904</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3176,32 +3176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>210034</t>
+          <t>232458</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>98644</t>
+          <t>207237</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>308308</t>
+          <t>257183</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>45,86%</t>
         </is>
       </c>
     </row>
@@ -3219,32 +3219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>61778</t>
+          <t>71245</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>47193</t>
+          <t>55014</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>80748</t>
+          <t>89699</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>24,79%</t>
+          <t>24,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3254,32 +3254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>24607</t>
+          <t>30052</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>62105</t>
+          <t>41124</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3289,32 +3289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>86385</t>
+          <t>101297</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>35531</t>
+          <t>83196</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>128099</t>
+          <t>122167</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -3332,32 +3332,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>28419</t>
+          <t>31728</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>20953</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>44890</t>
+          <t>48768</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3367,32 +3367,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6937</t>
+          <t>10399</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>5561</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>18625</t>
+          <t>17700</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3402,32 +3402,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>35355</t>
+          <t>42127</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>28677</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>57928</t>
+          <t>61206</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -3445,32 +3445,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>12057</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>4050</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>16849</t>
+          <t>22428</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,32 +3480,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>3851</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>753</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>13439</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>15908</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2781</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>21828</t>
+          <t>27365</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -3558,32 +3558,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>13554</t>
+          <t>14870</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>7104</t>
+          <t>8492</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24170</t>
+          <t>25408</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3593,7 +3593,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3603,12 +3603,12 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>6295</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>14598</t>
+          <t>15930</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4352</t>
+          <t>8858</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>26953</t>
+          <t>25186</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>7736</t>
+          <t>6737</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6374</t>
+          <t>6663</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>951</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>5295</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>951</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>6434</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3897,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>7994</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -4010,17 +4010,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>325735</t>
+          <t>360418</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>325735</t>
+          <t>360418</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>325735</t>
+          <t>360418</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>375434</t>
+          <t>200425</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>375434</t>
+          <t>200425</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>375434</t>
+          <t>200425</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4080,17 +4080,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>701169</t>
+          <t>560844</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>701169</t>
+          <t>560844</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>701169</t>
+          <t>560844</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4127,32 +4127,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>99255</t>
+          <t>101244</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>81983</t>
+          <t>83719</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>117805</t>
+          <t>120331</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4162,32 +4162,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>137823</t>
+          <t>140209</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>122975</t>
+          <t>124077</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>153895</t>
+          <t>155535</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>45,53%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>53,36%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4197,32 +4197,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>237078</t>
+          <t>241453</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>215422</t>
+          <t>219396</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>263893</t>
+          <t>268680</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>36,26%</t>
+          <t>34,93%</t>
         </is>
       </c>
     </row>
@@ -4240,32 +4240,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>161251</t>
+          <t>169986</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>141368</t>
+          <t>150137</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>179758</t>
+          <t>192345</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4275,32 +4275,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>76309</t>
+          <t>81893</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>63066</t>
+          <t>68744</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>89247</t>
+          <t>95464</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4310,32 +4310,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>237560</t>
+          <t>251879</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>214139</t>
+          <t>226501</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>261470</t>
+          <t>281092</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,54%</t>
         </is>
       </c>
     </row>
@@ -4353,32 +4353,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>95126</t>
+          <t>101504</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>77293</t>
+          <t>83064</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>116878</t>
+          <t>120516</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>18,01%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4388,32 +4388,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>49695</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>34235</t>
+          <t>39098</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>57203</t>
+          <t>63339</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4423,32 +4423,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>140154</t>
+          <t>151199</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>118976</t>
+          <t>129228</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>162599</t>
+          <t>174170</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,64%</t>
         </is>
       </c>
     </row>
@@ -4466,32 +4466,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>29634</t>
+          <t>31062</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>19594</t>
+          <t>21033</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>42352</t>
+          <t>45614</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4501,32 +4501,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>14485</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>19608</t>
+          <t>23578</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4536,32 +4536,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>41338</t>
+          <t>45547</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>29891</t>
+          <t>33576</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>56075</t>
+          <t>61499</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -4579,32 +4579,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>25143</t>
+          <t>27498</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>16068</t>
+          <t>17267</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>40002</t>
+          <t>41667</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4614,22 +4614,22 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>6565</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>2762</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>15127</t>
+          <t>15197</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4649,32 +4649,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>31708</t>
+          <t>34404</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>21509</t>
+          <t>23390</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>47189</t>
+          <t>52136</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -4692,32 +4692,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>20229</t>
+          <t>21327</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>12413</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>31091</t>
+          <t>32391</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4727,32 +4727,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>7067</t>
+          <t>9456</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2772</t>
+          <t>3781</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>16573</t>
+          <t>21331</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4762,32 +4762,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>27296</t>
+          <t>30783</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>20745</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>38276</t>
+          <t>45555</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,92%</t>
         </is>
       </c>
     </row>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4850,12 +4850,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>2748</t>
+          <t>4140</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>4895</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>659</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>3660</t>
+          <t>3234</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4988,7 +4988,7 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>659</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,5%</t>
         </is>
       </c>
     </row>
@@ -5031,22 +5031,22 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>3829</t>
+          <t>4007</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>14935</t>
+          <t>15873</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5066,32 +5066,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>3305</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>971</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>8605</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5101,32 +5101,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>11229</t>
+          <t>12122</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>6527</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>19569</t>
+          <t>21271</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -5144,17 +5144,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>439284</t>
+          <t>461314</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>439284</t>
+          <t>461314</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>439284</t>
+          <t>461314</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5179,17 +5179,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>288418</t>
+          <t>307931</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>288418</t>
+          <t>307931</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>288418</t>
+          <t>307931</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>727702</t>
+          <t>769245</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>727702</t>
+          <t>769245</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>727702</t>
+          <t>769245</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5261,32 +5261,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>345748</t>
+          <t>351699</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>307992</t>
+          <t>316305</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>387547</t>
+          <t>393846</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5296,32 +5296,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>548737</t>
+          <t>365973</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>422717</t>
+          <t>336674</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>751416</t>
+          <t>391794</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>41,27%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>73,35%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5331,32 +5331,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>894485</t>
+          <t>717672</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>733316</t>
+          <t>671430</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1398915</t>
+          <t>764239</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>34,46%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -5374,32 +5374,32 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>637828</t>
+          <t>684819</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>592431</t>
+          <t>637074</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>681719</t>
+          <t>729414</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>40,6%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,61%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5409,32 +5409,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>262191</t>
+          <t>290144</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>265998</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>336556</t>
+          <t>314606</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5444,32 +5444,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>900019</t>
+          <t>974964</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>657914</t>
+          <t>924903</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>997132</t>
+          <t>1024075</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>39,74%</t>
         </is>
       </c>
     </row>
@@ -5487,32 +5487,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>326676</t>
+          <t>359318</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>293479</t>
+          <t>321521</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>366401</t>
+          <t>397613</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5522,32 +5522,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>129762</t>
+          <t>147412</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>75521</t>
+          <t>125658</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>168930</t>
+          <t>169337</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5557,32 +5557,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>456438</t>
+          <t>506730</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>324634</t>
+          <t>462763</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>508338</t>
+          <t>545200</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -5600,32 +5600,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>116683</t>
+          <t>115279</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>93262</t>
+          <t>94295</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>153409</t>
+          <t>140892</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5635,32 +5635,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>28964</t>
+          <t>36449</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>25681</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>42022</t>
+          <t>49706</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5670,32 +5670,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>145647</t>
+          <t>151728</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>108593</t>
+          <t>126411</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>180258</t>
+          <t>180426</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -5713,32 +5713,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>61524</t>
+          <t>73362</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>46504</t>
+          <t>56476</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>81747</t>
+          <t>96467</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5748,32 +5748,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>25222</t>
+          <t>27966</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>11463</t>
+          <t>19765</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>38885</t>
+          <t>41932</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5783,32 +5783,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>86746</t>
+          <t>101329</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>63380</t>
+          <t>82515</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>109674</t>
+          <t>126459</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -5826,32 +5826,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>51811</t>
+          <t>55075</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>37982</t>
+          <t>41762</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>68339</t>
+          <t>75899</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5861,32 +5861,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>20863</t>
+          <t>25710</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>32913</t>
+          <t>39184</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5896,32 +5896,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>72673</t>
+          <t>80784</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>53457</t>
+          <t>63230</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>93757</t>
+          <t>103405</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -5939,32 +5939,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>5554</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2363</t>
+          <t>2615</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>10604</t>
+          <t>11750</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5974,32 +5974,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>1173</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>9051</t>
+          <t>11128</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6009,32 +6009,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>10557</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>16382</t>
+          <t>17979</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -6052,32 +6052,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2670</t>
+          <t>2733</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>13399</t>
+          <t>14761</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6122,32 +6122,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6811</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2930</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>15099</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -6165,32 +6165,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>20553</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>12197</t>
+          <t>13590</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>28274</t>
+          <t>30474</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6200,32 +6200,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>4696</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>12726</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6235,32 +6235,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>26187</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>33648</t>
+          <t>38236</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -6278,17 +6278,17 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>1571044</t>
+          <t>1672597</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6313,17 +6313,17 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>1024368</t>
+          <t>904165</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6348,17 +6348,17 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>2595413</t>
+          <t>2576762</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
